--- a/direct/model_outputs/aov1_formatted.xlsx
+++ b/direct/model_outputs/aov1_formatted.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rtbat\Dropbox\Agri_Contaminants\direct\model_outputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{CEFE82DF-9D50-4253-85A7-04189A919E46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D24192DE-85CA-4C15-BB9F-AA445E5C638D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-10920" yWindow="-21720" windowWidth="51840" windowHeight="21120" xr2:uid="{08EC239A-800E-4661-893A-671F4FE59C0F}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{08EC239A-800E-4661-893A-671F4FE59C0F}"/>
   </bookViews>
   <sheets>
     <sheet name="aov1" sheetId="1" r:id="rId1"/>
